--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,925 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122984911</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Södermossrudan, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>713479</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6659369</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122984922</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90380</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Södermossrudan, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>713452</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6659441</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122984913</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Södermossrudan, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>713513</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6659311</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122984914</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Södermossrudan, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>713682</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6659187</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122984919</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Södermossrudan, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>713681</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6659201</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122984918</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Södermossrudan, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>713503</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6659303</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122984924</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100623</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Södermossrudan, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>713474</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6659294</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122984923</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100623</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Södermossrudan, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>713441</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6659434</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122984910</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Södermossrudan, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>713447</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6659423</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122984911</v>
+        <v>122984923</v>
       </c>
       <c r="B3" t="n">
-        <v>97311</v>
+        <v>100623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713479</v>
+        <v>713441</v>
       </c>
       <c r="R3" t="n">
-        <v>6659369</v>
+        <v>6659434</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122984922</v>
+        <v>122984914</v>
       </c>
       <c r="B4" t="n">
-        <v>90380</v>
+        <v>97311</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,25 +905,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2008</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713452</v>
+        <v>713682</v>
       </c>
       <c r="R4" t="n">
-        <v>6659441</v>
+        <v>6659187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122984913</v>
+        <v>122984919</v>
       </c>
       <c r="B5" t="n">
-        <v>97311</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713513</v>
+        <v>713681</v>
       </c>
       <c r="R5" t="n">
-        <v>6659311</v>
+        <v>6659201</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122984914</v>
+        <v>122984918</v>
       </c>
       <c r="B6" t="n">
-        <v>97311</v>
+        <v>98379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713682</v>
+        <v>713503</v>
       </c>
       <c r="R6" t="n">
-        <v>6659187</v>
+        <v>6659303</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122984919</v>
+        <v>122984924</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>100623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713681</v>
+        <v>713474</v>
       </c>
       <c r="R7" t="n">
-        <v>6659201</v>
+        <v>6659294</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122984918</v>
+        <v>122984922</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>90380</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1313,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>2008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713503</v>
+        <v>713452</v>
       </c>
       <c r="R8" t="n">
-        <v>6659303</v>
+        <v>6659441</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,6 +1385,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122984924</v>
+        <v>122984910</v>
       </c>
       <c r="B9" t="n">
-        <v>100623</v>
+        <v>56688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713474</v>
+        <v>713447</v>
       </c>
       <c r="R9" t="n">
-        <v>6659294</v>
+        <v>6659423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122984923</v>
+        <v>122984913</v>
       </c>
       <c r="B10" t="n">
-        <v>100623</v>
+        <v>97311</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713441</v>
+        <v>713513</v>
       </c>
       <c r="R10" t="n">
-        <v>6659434</v>
+        <v>6659311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122984910</v>
+        <v>122984911</v>
       </c>
       <c r="B11" t="n">
-        <v>56688</v>
+        <v>97311</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713447</v>
+        <v>713479</v>
       </c>
       <c r="R11" t="n">
-        <v>6659423</v>
+        <v>6659369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122984923</v>
+        <v>122984918</v>
       </c>
       <c r="B3" t="n">
-        <v>100623</v>
+        <v>98387</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713441</v>
+        <v>713503</v>
       </c>
       <c r="R3" t="n">
-        <v>6659434</v>
+        <v>6659303</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122984914</v>
+        <v>122984923</v>
       </c>
       <c r="B4" t="n">
-        <v>97311</v>
+        <v>100631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713682</v>
+        <v>713441</v>
       </c>
       <c r="R4" t="n">
-        <v>6659187</v>
+        <v>6659434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122984919</v>
+        <v>122984910</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713681</v>
+        <v>713447</v>
       </c>
       <c r="R5" t="n">
-        <v>6659201</v>
+        <v>6659423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122984918</v>
+        <v>122984911</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>97319</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713503</v>
+        <v>713479</v>
       </c>
       <c r="R6" t="n">
-        <v>6659303</v>
+        <v>6659369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122984924</v>
+        <v>122984914</v>
       </c>
       <c r="B7" t="n">
-        <v>100623</v>
+        <v>97319</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713474</v>
+        <v>713682</v>
       </c>
       <c r="R7" t="n">
-        <v>6659294</v>
+        <v>6659187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
         <v>122984922</v>
       </c>
       <c r="B8" t="n">
-        <v>90380</v>
+        <v>90388</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122984910</v>
+        <v>122984924</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>100631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713447</v>
+        <v>713474</v>
       </c>
       <c r="R9" t="n">
-        <v>6659423</v>
+        <v>6659294</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122984913</v>
+        <v>122984919</v>
       </c>
       <c r="B10" t="n">
-        <v>97311</v>
+        <v>98387</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713513</v>
+        <v>713681</v>
       </c>
       <c r="R10" t="n">
-        <v>6659311</v>
+        <v>6659201</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122984911</v>
+        <v>122984913</v>
       </c>
       <c r="B11" t="n">
-        <v>97311</v>
+        <v>97319</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713479</v>
+        <v>713513</v>
       </c>
       <c r="R11" t="n">
-        <v>6659369</v>
+        <v>6659311</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122984918</v>
+        <v>122984910</v>
       </c>
       <c r="B3" t="n">
-        <v>98387</v>
+        <v>56688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713503</v>
+        <v>713447</v>
       </c>
       <c r="R3" t="n">
-        <v>6659303</v>
+        <v>6659423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122984910</v>
+        <v>122984914</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>97319</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713447</v>
+        <v>713682</v>
       </c>
       <c r="R5" t="n">
-        <v>6659423</v>
+        <v>6659187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122984911</v>
+        <v>122984919</v>
       </c>
       <c r="B6" t="n">
-        <v>97319</v>
+        <v>98387</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713479</v>
+        <v>713681</v>
       </c>
       <c r="R6" t="n">
-        <v>6659369</v>
+        <v>6659201</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122984914</v>
+        <v>122984911</v>
       </c>
       <c r="B7" t="n">
         <v>97319</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713682</v>
+        <v>713479</v>
       </c>
       <c r="R7" t="n">
-        <v>6659187</v>
+        <v>6659369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122984922</v>
+        <v>122984924</v>
       </c>
       <c r="B8" t="n">
-        <v>90388</v>
+        <v>100631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,25 +1313,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713452</v>
+        <v>713474</v>
       </c>
       <c r="R8" t="n">
-        <v>6659441</v>
+        <v>6659294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,7 +1385,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1404,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122984924</v>
+        <v>122984913</v>
       </c>
       <c r="B9" t="n">
-        <v>100631</v>
+        <v>97319</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713474</v>
+        <v>713513</v>
       </c>
       <c r="R9" t="n">
-        <v>6659294</v>
+        <v>6659311</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122984919</v>
+        <v>122984922</v>
       </c>
       <c r="B10" t="n">
-        <v>98387</v>
+        <v>90388</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1517,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>2008</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713681</v>
+        <v>713452</v>
       </c>
       <c r="R10" t="n">
-        <v>6659201</v>
+        <v>6659441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,6 +1589,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122984913</v>
+        <v>122984918</v>
       </c>
       <c r="B11" t="n">
-        <v>97319</v>
+        <v>98387</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713513</v>
+        <v>713503</v>
       </c>
       <c r="R11" t="n">
-        <v>6659311</v>
+        <v>6659303</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122984910</v>
+        <v>122984911</v>
       </c>
       <c r="B3" t="n">
-        <v>56688</v>
+        <v>97319</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713447</v>
+        <v>713479</v>
       </c>
       <c r="R3" t="n">
-        <v>6659423</v>
+        <v>6659369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122984914</v>
+        <v>122984919</v>
       </c>
       <c r="B5" t="n">
-        <v>97319</v>
+        <v>98387</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713682</v>
+        <v>713681</v>
       </c>
       <c r="R5" t="n">
-        <v>6659187</v>
+        <v>6659201</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122984919</v>
+        <v>122984913</v>
       </c>
       <c r="B6" t="n">
-        <v>98387</v>
+        <v>97319</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713681</v>
+        <v>713513</v>
       </c>
       <c r="R6" t="n">
-        <v>6659201</v>
+        <v>6659311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122984911</v>
+        <v>122984910</v>
       </c>
       <c r="B7" t="n">
-        <v>97319</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713479</v>
+        <v>713447</v>
       </c>
       <c r="R7" t="n">
-        <v>6659369</v>
+        <v>6659423</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122984924</v>
+        <v>122984914</v>
       </c>
       <c r="B8" t="n">
-        <v>100631</v>
+        <v>97319</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713474</v>
+        <v>713682</v>
       </c>
       <c r="R8" t="n">
-        <v>6659294</v>
+        <v>6659187</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122984913</v>
+        <v>122984922</v>
       </c>
       <c r="B9" t="n">
-        <v>97319</v>
+        <v>90388</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,25 +1415,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>2008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713513</v>
+        <v>713452</v>
       </c>
       <c r="R9" t="n">
-        <v>6659311</v>
+        <v>6659441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1487,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1505,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122984922</v>
+        <v>122984918</v>
       </c>
       <c r="B10" t="n">
-        <v>90388</v>
+        <v>98387</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2008</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713452</v>
+        <v>713503</v>
       </c>
       <c r="R10" t="n">
-        <v>6659441</v>
+        <v>6659303</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,7 +1590,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122984918</v>
+        <v>122984924</v>
       </c>
       <c r="B11" t="n">
-        <v>98387</v>
+        <v>100631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713503</v>
+        <v>713474</v>
       </c>
       <c r="R11" t="n">
-        <v>6659303</v>
+        <v>6659294</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122984911</v>
+        <v>122984913</v>
       </c>
       <c r="B3" t="n">
         <v>97319</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713479</v>
+        <v>713513</v>
       </c>
       <c r="R3" t="n">
-        <v>6659369</v>
+        <v>6659311</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122984923</v>
+        <v>122984910</v>
       </c>
       <c r="B4" t="n">
-        <v>100631</v>
+        <v>56688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713441</v>
+        <v>713447</v>
       </c>
       <c r="R4" t="n">
-        <v>6659434</v>
+        <v>6659423</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122984919</v>
+        <v>122984911</v>
       </c>
       <c r="B5" t="n">
-        <v>98387</v>
+        <v>97319</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713681</v>
+        <v>713479</v>
       </c>
       <c r="R5" t="n">
-        <v>6659201</v>
+        <v>6659369</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122984913</v>
+        <v>122984923</v>
       </c>
       <c r="B6" t="n">
-        <v>97319</v>
+        <v>100631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713513</v>
+        <v>713441</v>
       </c>
       <c r="R6" t="n">
-        <v>6659311</v>
+        <v>6659434</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122984910</v>
+        <v>122984914</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>97319</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713447</v>
+        <v>713682</v>
       </c>
       <c r="R7" t="n">
-        <v>6659423</v>
+        <v>6659187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122984914</v>
+        <v>122984919</v>
       </c>
       <c r="B8" t="n">
-        <v>97319</v>
+        <v>98387</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713682</v>
+        <v>713681</v>
       </c>
       <c r="R8" t="n">
-        <v>6659187</v>
+        <v>6659201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122984918</v>
+        <v>122984924</v>
       </c>
       <c r="B10" t="n">
-        <v>98387</v>
+        <v>100631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713503</v>
+        <v>713474</v>
       </c>
       <c r="R10" t="n">
-        <v>6659303</v>
+        <v>6659294</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122984924</v>
+        <v>122984918</v>
       </c>
       <c r="B11" t="n">
-        <v>100631</v>
+        <v>98387</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713474</v>
+        <v>713503</v>
       </c>
       <c r="R11" t="n">
-        <v>6659294</v>
+        <v>6659303</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122984919</v>
+        <v>122984922</v>
       </c>
       <c r="B8" t="n">
-        <v>98387</v>
+        <v>90388</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,25 +1313,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>2008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713681</v>
+        <v>713452</v>
       </c>
       <c r="R8" t="n">
-        <v>6659201</v>
+        <v>6659441</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,6 +1385,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1403,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122984922</v>
+        <v>122984919</v>
       </c>
       <c r="B9" t="n">
-        <v>90388</v>
+        <v>98387</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2008</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713452</v>
+        <v>713681</v>
       </c>
       <c r="R9" t="n">
-        <v>6659441</v>
+        <v>6659201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,7 +1488,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122984913</v>
+        <v>122984910</v>
       </c>
       <c r="B3" t="n">
-        <v>97319</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713513</v>
+        <v>713447</v>
       </c>
       <c r="R3" t="n">
-        <v>6659311</v>
+        <v>6659423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122984910</v>
+        <v>122984922</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>90391</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,25 +905,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>2008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713447</v>
+        <v>713452</v>
       </c>
       <c r="R4" t="n">
-        <v>6659423</v>
+        <v>6659441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122984911</v>
+        <v>122984923</v>
       </c>
       <c r="B5" t="n">
-        <v>97319</v>
+        <v>100634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713479</v>
+        <v>713441</v>
       </c>
       <c r="R5" t="n">
-        <v>6659369</v>
+        <v>6659434</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122984923</v>
+        <v>122984911</v>
       </c>
       <c r="B6" t="n">
-        <v>100631</v>
+        <v>97322</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713441</v>
+        <v>713479</v>
       </c>
       <c r="R6" t="n">
-        <v>6659434</v>
+        <v>6659369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1203,7 @@
         <v>122984914</v>
       </c>
       <c r="B7" t="n">
-        <v>97319</v>
+        <v>97322</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122984922</v>
+        <v>122984924</v>
       </c>
       <c r="B8" t="n">
-        <v>90388</v>
+        <v>100634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713452</v>
+        <v>713474</v>
       </c>
       <c r="R8" t="n">
-        <v>6659441</v>
+        <v>6659294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,7 +1386,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122984919</v>
+        <v>122984918</v>
       </c>
       <c r="B9" t="n">
-        <v>98387</v>
+        <v>98390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713681</v>
+        <v>713503</v>
       </c>
       <c r="R9" t="n">
-        <v>6659201</v>
+        <v>6659303</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122984924</v>
+        <v>122984913</v>
       </c>
       <c r="B10" t="n">
-        <v>100631</v>
+        <v>97322</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713474</v>
+        <v>713513</v>
       </c>
       <c r="R10" t="n">
-        <v>6659294</v>
+        <v>6659311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122984918</v>
+        <v>122984919</v>
       </c>
       <c r="B11" t="n">
-        <v>98387</v>
+        <v>98390</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713503</v>
+        <v>713681</v>
       </c>
       <c r="R11" t="n">
-        <v>6659303</v>
+        <v>6659201</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122984922</v>
+        <v>122984913</v>
       </c>
       <c r="B4" t="n">
-        <v>90391</v>
+        <v>97324</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,25 +905,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2008</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713452</v>
+        <v>713513</v>
       </c>
       <c r="R4" t="n">
-        <v>6659441</v>
+        <v>6659311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,7 +998,7 @@
         <v>122984923</v>
       </c>
       <c r="B5" t="n">
-        <v>100634</v>
+        <v>100636</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122984911</v>
+        <v>122984914</v>
       </c>
       <c r="B6" t="n">
-        <v>97322</v>
+        <v>97324</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713479</v>
+        <v>713682</v>
       </c>
       <c r="R6" t="n">
-        <v>6659369</v>
+        <v>6659187</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122984914</v>
+        <v>122984924</v>
       </c>
       <c r="B7" t="n">
-        <v>97322</v>
+        <v>100636</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713682</v>
+        <v>713474</v>
       </c>
       <c r="R7" t="n">
-        <v>6659187</v>
+        <v>6659294</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122984924</v>
+        <v>122984911</v>
       </c>
       <c r="B8" t="n">
-        <v>100634</v>
+        <v>97324</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713474</v>
+        <v>713479</v>
       </c>
       <c r="R8" t="n">
-        <v>6659294</v>
+        <v>6659369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1406,7 @@
         <v>122984918</v>
       </c>
       <c r="B9" t="n">
-        <v>98390</v>
+        <v>98392</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122984913</v>
+        <v>122984919</v>
       </c>
       <c r="B10" t="n">
-        <v>97322</v>
+        <v>98392</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1521,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713513</v>
+        <v>713681</v>
       </c>
       <c r="R10" t="n">
-        <v>6659311</v>
+        <v>6659201</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122984919</v>
+        <v>122984922</v>
       </c>
       <c r="B11" t="n">
-        <v>98390</v>
+        <v>90393</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1619,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>2008</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713681</v>
+        <v>713452</v>
       </c>
       <c r="R11" t="n">
-        <v>6659201</v>
+        <v>6659441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,6 +1691,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122984910</v>
+        <v>122984919</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>98398</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713447</v>
+        <v>713681</v>
       </c>
       <c r="R3" t="n">
-        <v>6659423</v>
+        <v>6659201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122984913</v>
+        <v>122984910</v>
       </c>
       <c r="B4" t="n">
-        <v>97324</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713513</v>
+        <v>713447</v>
       </c>
       <c r="R4" t="n">
-        <v>6659311</v>
+        <v>6659423</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122984923</v>
+        <v>122984914</v>
       </c>
       <c r="B5" t="n">
-        <v>100636</v>
+        <v>97330</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713441</v>
+        <v>713682</v>
       </c>
       <c r="R5" t="n">
-        <v>6659434</v>
+        <v>6659187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122984914</v>
+        <v>122984924</v>
       </c>
       <c r="B6" t="n">
-        <v>97324</v>
+        <v>100642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713682</v>
+        <v>713474</v>
       </c>
       <c r="R6" t="n">
-        <v>6659187</v>
+        <v>6659294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122984924</v>
+        <v>122984913</v>
       </c>
       <c r="B7" t="n">
-        <v>100636</v>
+        <v>97330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713474</v>
+        <v>713513</v>
       </c>
       <c r="R7" t="n">
-        <v>6659294</v>
+        <v>6659311</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122984911</v>
+        <v>122984923</v>
       </c>
       <c r="B8" t="n">
-        <v>97324</v>
+        <v>100642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713479</v>
+        <v>713441</v>
       </c>
       <c r="R8" t="n">
-        <v>6659369</v>
+        <v>6659434</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122984918</v>
+        <v>122984922</v>
       </c>
       <c r="B9" t="n">
-        <v>98392</v>
+        <v>90399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,25 +1415,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>2008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713503</v>
+        <v>713452</v>
       </c>
       <c r="R9" t="n">
-        <v>6659303</v>
+        <v>6659441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1487,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1505,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122984919</v>
+        <v>122984911</v>
       </c>
       <c r="B10" t="n">
-        <v>98392</v>
+        <v>97330</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713681</v>
+        <v>713479</v>
       </c>
       <c r="R10" t="n">
-        <v>6659201</v>
+        <v>6659369</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122984922</v>
+        <v>122984918</v>
       </c>
       <c r="B11" t="n">
-        <v>90393</v>
+        <v>98398</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2008</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713452</v>
+        <v>713503</v>
       </c>
       <c r="R11" t="n">
-        <v>6659441</v>
+        <v>6659303</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,7 +1692,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122984924</v>
+        <v>122984914</v>
       </c>
       <c r="B3" t="n">
-        <v>100645</v>
+        <v>97350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713474</v>
+        <v>713682</v>
       </c>
       <c r="R3" t="n">
-        <v>6659294</v>
+        <v>6659187</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122984919</v>
+        <v>122984923</v>
       </c>
       <c r="B4" t="n">
-        <v>98401</v>
+        <v>100662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713681</v>
+        <v>713441</v>
       </c>
       <c r="R4" t="n">
-        <v>6659201</v>
+        <v>6659434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122984913</v>
+        <v>122984924</v>
       </c>
       <c r="B5" t="n">
-        <v>97333</v>
+        <v>100662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713513</v>
+        <v>713474</v>
       </c>
       <c r="R5" t="n">
-        <v>6659311</v>
+        <v>6659294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122984911</v>
+        <v>122984910</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>56697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713479</v>
+        <v>713447</v>
       </c>
       <c r="R6" t="n">
-        <v>6659369</v>
+        <v>6659423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122984918</v>
+        <v>122984911</v>
       </c>
       <c r="B7" t="n">
-        <v>98401</v>
+        <v>97350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713503</v>
+        <v>713479</v>
       </c>
       <c r="R7" t="n">
-        <v>6659303</v>
+        <v>6659369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122984914</v>
+        <v>122984919</v>
       </c>
       <c r="B8" t="n">
-        <v>97333</v>
+        <v>98418</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713682</v>
+        <v>713681</v>
       </c>
       <c r="R8" t="n">
-        <v>6659187</v>
+        <v>6659201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122984923</v>
+        <v>122984913</v>
       </c>
       <c r="B9" t="n">
-        <v>100645</v>
+        <v>97350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713441</v>
+        <v>713513</v>
       </c>
       <c r="R9" t="n">
-        <v>6659434</v>
+        <v>6659311</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,7 +1508,7 @@
         <v>122984922</v>
       </c>
       <c r="B10" t="n">
-        <v>90402</v>
+        <v>90419</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122984910</v>
+        <v>122984918</v>
       </c>
       <c r="B11" t="n">
-        <v>56691</v>
+        <v>98418</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713447</v>
+        <v>713503</v>
       </c>
       <c r="R11" t="n">
-        <v>6659423</v>
+        <v>6659303</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122984911</v>
+        <v>122984919</v>
       </c>
       <c r="B7" t="n">
-        <v>97350</v>
+        <v>98418</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713479</v>
+        <v>713681</v>
       </c>
       <c r="R7" t="n">
-        <v>6659369</v>
+        <v>6659201</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122984919</v>
+        <v>122984911</v>
       </c>
       <c r="B8" t="n">
-        <v>98418</v>
+        <v>97350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713681</v>
+        <v>713479</v>
       </c>
       <c r="R8" t="n">
-        <v>6659201</v>
+        <v>6659369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 56792-2024 artfynd.xlsx
+++ b/artfynd/A 56792-2024 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122984919</v>
+        <v>122984911</v>
       </c>
       <c r="B7" t="n">
-        <v>98418</v>
+        <v>97350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713681</v>
+        <v>713479</v>
       </c>
       <c r="R7" t="n">
-        <v>6659201</v>
+        <v>6659369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122984911</v>
+        <v>122984919</v>
       </c>
       <c r="B8" t="n">
-        <v>97350</v>
+        <v>98418</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713479</v>
+        <v>713681</v>
       </c>
       <c r="R8" t="n">
-        <v>6659369</v>
+        <v>6659201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
